--- a/conformance/cases/xlsx-08-two-flows.xlsx
+++ b/conformance/cases/xlsx-08-two-flows.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Một" sheetId="1" r:id="rId1"/>
-    <sheet name="Hai" sheetId="2" r:id="rId2"/>
+    <sheet name="One" sheetId="1" r:id="rId1"/>
+    <sheet name="Two" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -90,7 +90,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bắt đầu</t>
+          <t xml:space="preserve">Start</t>
         </is>
       </c>
     </row>
@@ -107,7 +107,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">gửi yêu cầu</t>
+          <t xml:space="preserve">send request</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -134,7 +134,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xong sớm</t>
+          <t xml:space="preserve">Done early</t>
         </is>
       </c>
     </row>
@@ -224,7 +224,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bắt đầu</t>
+          <t xml:space="preserve">Start</t>
         </is>
       </c>
     </row>
@@ -241,7 +241,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">gửi yêu cầu</t>
+          <t xml:space="preserve">send request</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -268,7 +268,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xử lý</t>
+          <t xml:space="preserve">Process</t>
         </is>
       </c>
     </row>
@@ -307,7 +307,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xong</t>
+          <t xml:space="preserve">Done</t>
         </is>
       </c>
     </row>
